--- a/classifiche/Castelletto.xlsx
+++ b/classifiche/Castelletto.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t xml:space="preserve">Stagione</t>
   </si>
@@ -540,9 +540,7 @@
       <c r="F2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
@@ -586,9 +584,7 @@
       <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>

--- a/classifiche/Castelletto.xlsx
+++ b/classifiche/Castelletto.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t xml:space="preserve">Stagione</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">01:32.24</t>
+    <t xml:space="preserve">1:32.24</t>
   </si>
   <si>
     <t xml:space="preserve">Alessio</t>
@@ -73,10 +73,19 @@
     <t xml:space="preserve">https://www.youtube.com/watch?v=AW948qCoz34</t>
   </si>
   <si>
-    <t xml:space="preserve">119.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:39.23</t>
+    <t xml:space="preserve">120.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:38.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommaso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX-5 NB/FL 1.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:33.47</t>
   </si>
 </sst>
 </file>
@@ -590,12 +599,24 @@
       <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/classifiche/Castelletto.xlsx
+++ b/classifiche/Castelletto.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t xml:space="preserve">Stagione</t>
   </si>
@@ -86,6 +86,27 @@
   </si>
   <si>
     <t xml:space="preserve">1:33.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claudio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX-5 ND 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:42.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX-5 NC 2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:36.12</t>
   </si>
 </sst>
 </file>
@@ -620,21 +641,45 @@
       <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="A6" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
